--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.80414</v>
+        <v>16.80837</v>
       </c>
       <c r="D2" t="n">
-        <v>16.71883</v>
+        <v>16.49529</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45438</v>
+        <v>16.7276</v>
       </c>
       <c r="F2" t="n">
-        <v>42.45555</v>
+        <v>42.58335</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05118</v>
+        <v>0.05043</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8232</v>
+        <v>1.81276</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.73159</v>
+        <v>17.04658</v>
       </c>
       <c r="D3" t="n">
-        <v>16.41146</v>
+        <v>16.3661</v>
       </c>
       <c r="E3" t="n">
-        <v>16.60998</v>
+        <v>16.5183</v>
       </c>
       <c r="F3" t="n">
-        <v>41.67735</v>
+        <v>41.39838</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04985</v>
+        <v>0.05036</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81676</v>
+        <v>1.81011</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.78902</v>
+        <v>16.68325</v>
       </c>
       <c r="D4" t="n">
-        <v>16.59725</v>
+        <v>16.54356</v>
       </c>
       <c r="E4" t="n">
-        <v>16.70148</v>
+        <v>16.55893</v>
       </c>
       <c r="F4" t="n">
-        <v>42.80826</v>
+        <v>42.6208</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05144</v>
+        <v>0.05141</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78983</v>
+        <v>1.81851</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.45878</v>
+        <v>16.78979</v>
       </c>
       <c r="D6" t="n">
-        <v>16.22504</v>
+        <v>16.21853</v>
       </c>
       <c r="E6" t="n">
-        <v>16.28393</v>
+        <v>16.26115</v>
       </c>
       <c r="F6" t="n">
-        <v>21.41722</v>
+        <v>22.19491</v>
       </c>
       <c r="G6" t="n">
-        <v>34.36693</v>
+        <v>33.88917</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.57524</v>
+        <v>17.05161</v>
       </c>
       <c r="D7" t="n">
-        <v>15.90023</v>
+        <v>16.01705</v>
       </c>
       <c r="E7" t="n">
-        <v>16.68777</v>
+        <v>16.64797</v>
       </c>
       <c r="F7" t="n">
-        <v>21.75813</v>
+        <v>22.16363</v>
       </c>
       <c r="G7" t="n">
-        <v>34.50851</v>
+        <v>35.19589</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.61316</v>
+        <v>16.69343</v>
       </c>
       <c r="D8" t="n">
-        <v>15.85814</v>
+        <v>16.12283</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2765</v>
+        <v>16.20002</v>
       </c>
       <c r="F8" t="n">
-        <v>21.65576</v>
+        <v>22.57665</v>
       </c>
       <c r="G8" t="n">
-        <v>34.75683</v>
+        <v>33.87328</v>
       </c>
     </row>
   </sheetData>
